--- a/tests/testthat/fixtures/ref-kreise-umrech-2021-testfixture.xlsx
+++ b/tests/testthat/fixtures/ref-kreise-umrech-2021-testfixture.xlsx
@@ -17,34 +17,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="13">
   <si>
-    <t>KOPF1</t>
-  </si>
-  <si>
-    <t>KOPF2</t>
-  </si>
-  <si>
-    <t>KOPF3</t>
-  </si>
-  <si>
-    <t>KOPF4</t>
-  </si>
-  <si>
-    <t>KOPF5</t>
-  </si>
-  <si>
-    <t>KOPF6</t>
-  </si>
-  <si>
-    <t>KOPF7</t>
-  </si>
-  <si>
-    <t>KOPF8</t>
+    <t>HEAD1</t>
+  </si>
+  <si>
+    <t>HEAD2</t>
+  </si>
+  <si>
+    <t>HEAD3</t>
+  </si>
+  <si>
+    <t>HEAD4</t>
+  </si>
+  <si>
+    <t>HEAD5</t>
+  </si>
+  <si>
+    <t>HEAD6</t>
+  </si>
+  <si>
+    <t>HEAD7</t>
+  </si>
+  <si>
+    <t>HEAD8</t>
   </si>
   <si>
     <t>01000001</t>
   </si>
   <si>
-    <t>Kreis A</t>
+    <t>District A</t>
   </si>
   <si>
     <t>1</t>
